--- a/data/stats/supp_tables/fallcover-soilcover-anova.xlsx
+++ b/data/stats/supp_tables/fallcover-soilcover-anova.xlsx
@@ -11,6 +11,68 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>statistic</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>till_id</t>
+  </si>
+  <si>
+    <t>cctrt_id</t>
+  </si>
+  <si>
+    <t>straw_id</t>
+  </si>
+  <si>
+    <t>weayear</t>
+  </si>
+  <si>
+    <t>till_id:cctrt_id</t>
+  </si>
+  <si>
+    <t>till_id:straw_id</t>
+  </si>
+  <si>
+    <t>cctrt_id:straw_id</t>
+  </si>
+  <si>
+    <t>till_id:weayear</t>
+  </si>
+  <si>
+    <t>cctrt_id:weayear</t>
+  </si>
+  <si>
+    <t>straw_id:weayear</t>
+  </si>
+  <si>
+    <t>till_id:cctrt_id:straw_id</t>
+  </si>
+  <si>
+    <t>till_id:cctrt_id:weayear</t>
+  </si>
+  <si>
+    <t>till_id:straw_id:weayear</t>
+  </si>
+  <si>
+    <t>cctrt_id:straw_id:weayear</t>
+  </si>
+  <si>
+    <t>till_id:cctrt_id:straw_id:weayear</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,266 +416,228 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>till_id</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>21.2280976816977</v>
+        <v>21.22775700135434</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2.456841603746707E-05</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cctrt_id</t>
-        </is>
+        <v>2.457260138212884E-05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>133.2829854736133</v>
+        <v>133.2833912505257</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
-        <v>7.730020075308225E-28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>straw_id</t>
-        </is>
+        <v>7.72847508379628E-28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>0.7124971866158196</v>
+        <v>0.7124820655917318</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.3986160508979164</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>weayear</t>
-        </is>
+        <v>0.3986210556992396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>155.0108773362706</v>
+        <v>155.0097961795148</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1.392569086902961E-35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>till_id:cctrt_id</t>
-        </is>
+        <v>1.393326881425427E-35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>29.75000686888401</v>
+        <v>29.74983058299701</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.0002339979990172203</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>till_id:straw_id</t>
-        </is>
+        <v>0.0002340147596686122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>1.566125576448357</v>
+        <v>1.566063186450802</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0.4570041586566572</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cctrt_id:straw_id</t>
-        </is>
+        <v>0.4570184151231919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>4.121398941020738</v>
+        <v>4.121332053431958</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>0.3898255313231108</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>till_id:weayear</t>
-        </is>
+        <v>0.3898343090796981</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>3.922165514725838</v>
+        <v>3.922114129317543</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>0.1407059879675072</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cctrt_id:weayear</t>
-        </is>
+        <v>0.1407096031312693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>133.1568952851956</v>
+        <v>133.1576366294801</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10">
-        <v>8.225376507526926E-28</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>straw_id:weayear</t>
-        </is>
+        <v>8.222373254600624E-28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>13.92638572010555</v>
+        <v>13.92648214854488</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.0001901109104122836</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>till_id:cctrt_id:straw_id</t>
-        </is>
+        <v>0.0001901011580789504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
       </c>
       <c r="B12">
-        <v>15.75904347042919</v>
+        <v>15.75913770107525</v>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12">
-        <v>0.04596169110564145</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>till_id:cctrt_id:weayear</t>
-        </is>
+        <v>0.04596023741715465</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>44.12656978195129</v>
+        <v>44.12655523054906</v>
       </c>
       <c r="C13">
         <v>8</v>
       </c>
       <c r="D13">
-        <v>5.384709745907658E-07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>till_id:straw_id:weayear</t>
-        </is>
+        <v>5.384743847338553E-07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
       </c>
       <c r="B14">
-        <v>0.2255675001252959</v>
+        <v>0.2255989632670621</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>0.8933438247754816</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cctrt_id:straw_id:weayear</t>
-        </is>
+        <v>0.893329771184322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>3.365368270611158</v>
+        <v>3.365449526814402</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15">
-        <v>0.4986422875230337</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>till_id:cctrt_id:straw_id:weayear</t>
-        </is>
+        <v>0.4986295804619938</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>9.779537916902772</v>
+        <v>9.77946698066007</v>
       </c>
       <c r="C16">
         <v>8</v>
       </c>
       <c r="D16">
-        <v>0.2808417493752944</v>
+        <v>0.2808469487995159</v>
       </c>
     </row>
   </sheetData>
